--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_41_R5.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_41_R5.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4537</v>
+        <v>7.9517</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4908</v>
+        <v>5.9888</v>
       </c>
       <c r="F2" t="n">
         <v>1.9629</v>
@@ -610,10 +610,10 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5005</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1077</v>
+        <v>0.6058</v>
       </c>
       <c r="U2" t="n">
         <v>0.3927</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7292</v>
+        <v>4.3747</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2717</v>
+        <v>-0.0074</v>
       </c>
       <c r="F3" t="n">
-        <v>5.4575</v>
+        <v>4.3821</v>
       </c>
       <c r="G3" t="n">
         <v>0.2166</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2807</v>
+        <v>1.9261</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7591</v>
+        <v>0.4799</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5216</v>
+        <v>1.4462</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7796</v>
+        <v>3.9385</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4274</v>
+        <v>1.0486</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3522</v>
+        <v>2.8899</v>
       </c>
       <c r="G4" t="n">
         <v>4.8022</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6361</v>
+        <v>0.5228</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4007</v>
+        <v>0.2205</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2355</v>
+        <v>0.3023</v>
       </c>
       <c r="V4" t="n">
         <v>1.8608</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0172</v>
+        <v>2.178</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0229</v>
+        <v>2.3518</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0057</v>
+        <v>-0.1738</v>
       </c>
       <c r="G5" t="n">
         <v>2.5943</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5566</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1123</v>
+        <v>0.2166</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5557</v>
+        <v>0.3877</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7886</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0102</v>
+        <v>0.2307</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2483</v>
+        <v>0.5436</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2586</v>
+        <v>-0.3129</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0218</v>
+        <v>0.1688</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.443</v>
+        <v>1.7347</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5788</v>
+        <v>-1.5659</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7359</v>
+        <v>0.626</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7359</v>
+        <v>0.8234</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.1975</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2859</v>
+        <v>-0.4572</v>
       </c>
       <c r="N6" t="n">
-        <v>0.293</v>
+        <v>0.9113</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5788</v>
+        <v>-1.3684</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7099</v>
+        <v>-0.6339</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4876</v>
+        <v>-0.0824</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2223</v>
+        <v>-0.5515</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.2666</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3977</v>
+        <v>-0.1618</v>
       </c>
       <c r="F7" t="n">
         <v>-0.1049</v>
@@ -1000,10 +1000,10 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5465</v>
+        <v>-0.3106</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U7" t="n">
         <v>-0.0984</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.6289</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0462</v>
+        <v>-0.4842</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5481</v>
+        <v>-0.1447</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1688</v>
+        <v>-1.0218</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7347</v>
+        <v>-0.443</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5659</v>
+        <v>-0.5788</v>
       </c>
       <c r="J8" t="n">
-        <v>0.626</v>
+        <v>-0.7359</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8234</v>
+        <v>-0.7359</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1975</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4572</v>
+        <v>-0.2859</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9113</v>
+        <v>0.293</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3684</v>
+        <v>-0.5788</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4589</v>
+        <v>0.0707</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6721</v>
+        <v>0.2517</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.181</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.347</v>
+        <v>-2.2639</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.0765</v>
+        <v>-4.4304</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7295</v>
+        <v>2.1664</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5769</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1577</v>
+        <v>0.2407</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2636</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1059</v>
+        <v>0.331</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BERTANS</t>
+          <t>K. PREPELIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7933</v>
+        <v>-2.7932</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0283</v>
+        <v>-4.2733</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.765</v>
+        <v>1.4801</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0731</v>
+        <v>1.3694</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0048</v>
+        <v>1.801</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0684</v>
+        <v>-0.4316</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7053</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1659</v>
+        <v>1.0083</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5394</v>
+        <v>-0.3213</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3678</v>
+        <v>0.6824</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1611</v>
+        <v>0.7927</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.529</v>
+        <v>-0.1103</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R10" t="n">
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4938</v>
+        <v>-0.5004</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2284</v>
+        <v>-0.7466</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2653</v>
+        <v>0.2462</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.6468</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6083</v>
+        <v>0.4254</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2862</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. PREPELIC</t>
+          <t>D. BERTANS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0364</v>
+        <v>-3.2577</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0124</v>
+        <v>-2.4254</v>
       </c>
       <c r="F11" t="n">
-        <v>0.976</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3694</v>
+        <v>-3.0731</v>
       </c>
       <c r="H11" t="n">
-        <v>1.801</v>
+        <v>-0.0048</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4316</v>
+        <v>-3.0684</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6870000000000001</v>
+        <v>-2.7053</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0083</v>
+        <v>-1.1659</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3213</v>
+        <v>-1.5394</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6824</v>
+        <v>-0.3678</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7927</v>
+        <v>1.1611</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1103</v>
+        <v>-1.529</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.0154</v>
+        <v>0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7436</v>
+        <v>0.0294</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4857</v>
+        <v>-0.1687</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2579</v>
+        <v>0.1981</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6468</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0.4254</v>
+        <v>1.6083</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.7164</v>
+        <v>9.463300000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.596600000000001</v>
+        <v>-1.849699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>11.313</v>
+        <v>11.3129</v>
       </c>
       <c r="G12" t="n">
         <v>4.9173</v>
@@ -1363,7 +1363,7 @@
         <v>-6.3071</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1646</v>
+        <v>2.164600000000001</v>
       </c>
       <c r="K12" t="n">
         <v>3.437100000000001</v>
@@ -1378,7 +1378,7 @@
         <v>7.7874</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.0347</v>
+        <v>-5.034700000000001</v>
       </c>
       <c r="P12" t="n">
         <v>-3.479200000000001</v>
@@ -1390,13 +1390,13 @@
         <v>10.438</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2009</v>
+        <v>2.9476</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2725000000000002</v>
+        <v>0.4743000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4731</v>
+        <v>2.4733</v>
       </c>
       <c r="V12" t="n">
         <v>5.077400000000001</v>
@@ -1405,7 +1405,7 @@
         <v>9.4284</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.351000000000001</v>
+        <v>-4.351</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7483</v>
+        <v>2.8117</v>
       </c>
       <c r="E13" t="n">
-        <v>2.094</v>
+        <v>1.5042</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6543</v>
+        <v>1.3074</v>
       </c>
       <c r="G13" t="n">
         <v>2.5567</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5705</v>
+        <v>0.6339</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6923</v>
+        <v>0.1026</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8782</v>
+        <v>0.5313</v>
       </c>
       <c r="V13" t="n">
         <v>-2.0026</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3609</v>
+        <v>1.9936</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2289</v>
+        <v>2.3582</v>
       </c>
       <c r="F14" t="n">
-        <v>1.132</v>
+        <v>-0.3646</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5946</v>
+        <v>1.6409</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.299</v>
+        <v>-0.39</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8936</v>
+        <v>2.0309</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4418</v>
+        <v>2.6881</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5952</v>
+        <v>-0.4502</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8467</v>
+        <v>3.1383</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8472</v>
+        <v>-1.0472</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8942</v>
+        <v>0.0602</v>
       </c>
       <c r="O14" t="n">
-        <v>0.047</v>
+        <v>-1.1074</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2337</v>
+        <v>-0.4334</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.963</v>
+        <v>-0.098</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7292</v>
+        <v>-0.3354</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>-0.1418</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2408</v>
+        <v>1.9406</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1537</v>
+        <v>1.0546</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0871</v>
+        <v>0.886</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8736</v>
+        <v>1.5946</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5222</v>
+        <v>-0.299</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3513</v>
+        <v>1.8936</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5914</v>
+        <v>2.4418</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5546</v>
+        <v>0.5952</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0368</v>
+        <v>1.8467</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2822</v>
+        <v>-0.8472</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0323</v>
+        <v>-0.8942</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3145</v>
+        <v>0.047</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R15" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1353</v>
+        <v>0.3459</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5623</v>
+        <v>-0.1373</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.427</v>
+        <v>0.4832</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0506</v>
+        <v>1.0721</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6505</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5998</v>
+        <v>0.1544</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6409</v>
+        <v>0.8736</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.39</v>
+        <v>0.5222</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0309</v>
+        <v>0.3513</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6881</v>
+        <v>0.5914</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4502</v>
+        <v>0.5546</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1383</v>
+        <v>0.0368</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0472</v>
+        <v>0.2822</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0602</v>
+        <v>-0.0323</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1074</v>
+        <v>0.3145</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3763</v>
+        <v>-0.0334</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8057</v>
+        <v>0.3264</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5706</v>
+        <v>-0.3598</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.545</v>
+        <v>0.6794</v>
       </c>
       <c r="E17" t="n">
         <v>0.8276</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2825</v>
+        <v>-0.1481</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9267</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3453</v>
+        <v>0.4797</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0351</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3804</v>
+        <v>0.5149</v>
       </c>
       <c r="V17" t="n">
         <v>2.2862</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2084</v>
+        <v>0.1511</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1471</v>
+        <v>1.383</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3555</v>
+        <v>-1.2318</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6395</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0328</v>
+        <v>-0.6732</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1791</v>
+        <v>-0.9432</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1463</v>
+        <v>0.27</v>
       </c>
       <c r="V18" t="n">
         <v>0.5361</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2087</v>
+        <v>0.1089</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5174</v>
+        <v>-1.3982</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3087</v>
+        <v>1.5072</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0041</v>
+        <v>-0.5965</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.144</v>
+        <v>0.4407</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1481</v>
+        <v>-1.0372</v>
       </c>
       <c r="J19" t="n">
-        <v>0.043</v>
+        <v>-0.8717</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9005</v>
+        <v>0.3697</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9435</v>
+        <v>-1.2414</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9611</v>
+        <v>0.2753</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2435</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2046</v>
+        <v>0.2042</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3725</v>
+        <v>-0.0806</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4007</v>
+        <v>-0.2946</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0281</v>
+        <v>0.2139</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8068</v>
+        <v>0.0323</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2239</v>
+        <v>-1.6354</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4171</v>
+        <v>1.6677</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5965</v>
+        <v>1.0041</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4407</v>
+        <v>-1.144</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0372</v>
+        <v>2.1481</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8717</v>
+        <v>0.043</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3697</v>
+        <v>-0.9005</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2414</v>
+        <v>0.9435</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2753</v>
+        <v>0.9611</v>
       </c>
       <c r="N20" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.2435</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2042</v>
+        <v>1.2046</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9963</v>
+        <v>-0.1316</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1202</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1239</v>
+        <v>0.387</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8379</v>
+        <v>-1.4105</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1177</v>
+        <v>-0.3541</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9556</v>
+        <v>-1.0564</v>
       </c>
       <c r="G21" t="n">
         <v>0.6002</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7938</v>
+        <v>0.2212</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4876</v>
+        <v>0.0158</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2331</v>
+        <v>-3.8571</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0504</v>
+        <v>-3.876</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1827</v>
+        <v>0.0189</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1832</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>0.347</v>
+        <v>-0.277</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6256</v>
+        <v>-0.2001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2785</v>
+        <v>-0.0769</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8608</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4012</v>
+        <v>-5.2088</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7689</v>
+        <v>-6.5458</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6324</v>
+        <v>1.3369</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4358</v>
+        <v>-4.4058</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.8909</v>
+        <v>-3.3084</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4551</v>
+        <v>-1.0975</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.6106</v>
+        <v>-4.4732</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.6474</v>
+        <v>-3.0109</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0368</v>
+        <v>-1.4623</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1748</v>
+        <v>0.0674</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2435</v>
+        <v>-0.2974</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4183</v>
+        <v>0.3648</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5553</v>
+        <v>-1.1793</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8417</v>
+        <v>-0.8252</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2864</v>
+        <v>-0.3541</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.6805</v>
+        <v>1.0722</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9659</v>
+        <v>-6.2434</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.8996</v>
+        <v>-4.4766</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9337</v>
+        <v>-1.7668</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.4058</v>
+        <v>-4.4358</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.3084</v>
+        <v>-4.8909</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0975</v>
+        <v>0.4551</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.4732</v>
+        <v>-4.6106</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.0109</v>
+        <v>-4.6474</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4623</v>
+        <v>0.0368</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0674</v>
+        <v>0.1748</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2974</v>
+        <v>-0.2435</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3648</v>
+        <v>0.4183</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9364</v>
+        <v>-0.2869</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1791</v>
+        <v>0.134</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7573</v>
+        <v>-0.4208</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0722</v>
+        <v>-2.6805</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.716400000000002</v>
+        <v>-7.9301</v>
       </c>
       <c r="E25" t="n">
         <v>-10.2407</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5244</v>
+        <v>2.3108</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.917400000000001</v>
+        <v>-4.917399999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-11.2246</v>
@@ -2383,7 +2383,7 @@
         <v>-7.7873</v>
       </c>
       <c r="L25" t="n">
-        <v>5.034700000000001</v>
+        <v>5.034699999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-2.1646</v>
@@ -2404,16 +2404,16 @@
         <v>13.9173</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.200800000000001</v>
+        <v>-1.4147</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.4734</v>
+        <v>-2.4733</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2725000000000001</v>
+        <v>1.0587</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.077399999999999</v>
+        <v>-5.0774</v>
       </c>
       <c r="W25" t="n">
         <v>5.4231</v>
